--- a/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
@@ -641,17 +641,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,36</t>
+          <t>-0,88; 1,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-2,51; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 0,72</t>
+          <t>-0,46; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,27</t>
+          <t>0,0; 1,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,57</t>
+          <t>0,0; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 0,75</t>
+          <t>-1,35; 0,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,31</t>
+          <t>-1,36; 1,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,38</t>
+          <t>-0,68; 0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,66</t>
+          <t>-0,67; 0,67</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,34</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,39</t>
+          <t>-0,48; 0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,28</t>
+          <t>-0,57; 0,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,3</t>
+          <t>-0,22; 0,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,14</t>
+          <t>-0,3; 0,13</t>
         </is>
       </c>
     </row>
@@ -1341,7 +1341,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-86,04; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
@@ -641,12 +641,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 1,35</t>
+          <t>-0,9; 1,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 0,0</t>
+          <t>-2,19; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 0,0</t>
+          <t>-1,26; 0,0</t>
         </is>
       </c>
     </row>
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,61</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 0,77</t>
+          <t>-1,4; 0,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,3</t>
+          <t>-1,37; 1,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,38</t>
+          <t>-0,82; 0,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,67</t>
+          <t>-0,67; 0,65</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,34</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1265,22 +1265,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 0,41</t>
+          <t>-0,5; 0,36</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 0,27</t>
+          <t>-0,59; 0,26</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,27</t>
+          <t>-0,23; 0,25</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 0,13</t>
+          <t>-0,3; 0,14</t>
         </is>
       </c>
     </row>
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">

--- a/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1015-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-0,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-0,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,3; 1,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 0,72</t>
+          <t>-0,69; 0,72</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,0</t>
+          <t>-1,16; 0,0</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,17 +749,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -797,7 +797,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -807,7 +807,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -825,17 +825,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,85</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -981,17 +981,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,64; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,42; 1,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,37</t>
+          <t>-0,82; 0,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 0,65</t>
+          <t>-0,67; 0,66</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-46,47%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-1,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-46,47%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-1,66%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-0,01</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0,07</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,01</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,1</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,27 +1255,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>-0,48; 0,39</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>-0,57; 0,28</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>-0,5; 0,36</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,26</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 0,25</t>
+          <t>-0,21; 0,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-4,92%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-36,2%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-4,92%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-36,2%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>-86,04; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
